--- a/DBs/wnba/Results/WNBA_2021_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2021_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70DB481-7C51-46E1-ABB2-4F521C0C94FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656B1D4E-EB25-4BBE-A21C-F2A6E7C51B88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2066" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="28">
   <si>
     <t>Date</t>
   </si>
@@ -121,6 +121,9 @@
   <si>
     <t>P</t>
   </si>
+  <si>
+    <t>N</t>
+  </si>
 </sst>
 </file>
 
@@ -179,8 +182,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}" name="Table1" displayName="Table1" ref="A1:J419" totalsRowShown="0">
-  <autoFilter ref="A1:J419" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}" name="Table1" displayName="Table1" ref="A1:J421" totalsRowShown="0">
+  <autoFilter ref="A1:J421" xr:uid="{6761A9D6-0284-4780-BB0F-50A0FFF04726}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9606CA38-2371-480A-B2F8-3A23285B655E}" name="Date" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{B29C85CC-3DBC-401B-A183-ABA3F92B96B9}" name="Season"/>
@@ -514,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FB24B2-7646-4F57-8F9C-DF3DFCDB2AF4}">
-  <dimension ref="A1:J419"/>
+  <dimension ref="A1:J421"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.9140625" bestFit="1" customWidth="1"/>
@@ -8178,66 +8181,66 @@
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
-        <v>44423</v>
+        <v>44420</v>
       </c>
       <c r="B240">
         <v>2021</v>
       </c>
       <c r="C240" t="s">
-        <v>10</v>
-      </c>
-      <c r="D240" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D240">
+        <v>0.1</v>
       </c>
       <c r="E240" t="s">
         <v>17</v>
       </c>
       <c r="F240" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G240" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H240">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I240">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="J240">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
-        <v>44423</v>
+        <v>44420</v>
       </c>
       <c r="B241">
         <v>2021</v>
       </c>
       <c r="C241" t="s">
-        <v>10</v>
-      </c>
-      <c r="D241" t="s">
-        <v>11</v>
+        <v>26</v>
+      </c>
+      <c r="D241">
+        <v>0.1</v>
       </c>
       <c r="E241" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F241" t="s">
         <v>17</v>
       </c>
       <c r="G241" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H241">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="I241">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="J241">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.35">
@@ -8254,22 +8257,22 @@
         <v>11</v>
       </c>
       <c r="E242" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F242" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G242" t="s">
         <v>24</v>
       </c>
       <c r="H242">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I242">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="J242">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.35">
@@ -8286,22 +8289,22 @@
         <v>11</v>
       </c>
       <c r="E243" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F243" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G243" t="s">
         <v>25</v>
       </c>
       <c r="H243">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="I243">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J243">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.35">
@@ -8318,19 +8321,19 @@
         <v>11</v>
       </c>
       <c r="E244" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F244" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G244" t="s">
         <v>24</v>
       </c>
       <c r="H244">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="I244">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="J244">
         <v>0</v>
@@ -8350,19 +8353,19 @@
         <v>11</v>
       </c>
       <c r="E245" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F245" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G245" t="s">
         <v>25</v>
       </c>
       <c r="H245">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="I245">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J245">
         <v>0</v>
@@ -8382,19 +8385,19 @@
         <v>11</v>
       </c>
       <c r="E246" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F246" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G246" t="s">
         <v>24</v>
       </c>
       <c r="H246">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="I246">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="J246">
         <v>0</v>
@@ -8414,19 +8417,19 @@
         <v>11</v>
       </c>
       <c r="E247" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F247" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G247" t="s">
         <v>25</v>
       </c>
       <c r="H247">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I247">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="J247">
         <v>0</v>
@@ -8446,19 +8449,19 @@
         <v>11</v>
       </c>
       <c r="E248" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F248" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G248" t="s">
         <v>24</v>
       </c>
       <c r="H248">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I248">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J248">
         <v>0</v>
@@ -8478,19 +8481,19 @@
         <v>11</v>
       </c>
       <c r="E249" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F249" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G249" t="s">
         <v>25</v>
       </c>
       <c r="H249">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I249">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J249">
         <v>0</v>
@@ -8510,19 +8513,19 @@
         <v>11</v>
       </c>
       <c r="E250" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F250" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G250" t="s">
         <v>24</v>
       </c>
       <c r="H250">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I250">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J250">
         <v>0</v>
@@ -8542,19 +8545,19 @@
         <v>11</v>
       </c>
       <c r="E251" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F251" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G251" t="s">
         <v>25</v>
       </c>
       <c r="H251">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I251">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J251">
         <v>0</v>
@@ -8562,7 +8565,7 @@
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
-        <v>44425</v>
+        <v>44423</v>
       </c>
       <c r="B252">
         <v>2021</v>
@@ -8574,19 +8577,19 @@
         <v>11</v>
       </c>
       <c r="E252" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F252" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G252" t="s">
         <v>24</v>
       </c>
       <c r="H252">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I252">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="J252">
         <v>0</v>
@@ -8594,7 +8597,7 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
-        <v>44425</v>
+        <v>44423</v>
       </c>
       <c r="B253">
         <v>2021</v>
@@ -8606,19 +8609,19 @@
         <v>11</v>
       </c>
       <c r="E253" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F253" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G253" t="s">
         <v>25</v>
       </c>
       <c r="H253">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="I253">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J253">
         <v>0</v>
@@ -8638,19 +8641,19 @@
         <v>11</v>
       </c>
       <c r="E254" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F254" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G254" t="s">
         <v>24</v>
       </c>
       <c r="H254">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I254">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J254">
         <v>0</v>
@@ -8670,19 +8673,19 @@
         <v>11</v>
       </c>
       <c r="E255" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F255" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G255" t="s">
         <v>25</v>
       </c>
       <c r="H255">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="I255">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="J255">
         <v>0</v>
@@ -8702,22 +8705,22 @@
         <v>11</v>
       </c>
       <c r="E256" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F256" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G256" t="s">
         <v>24</v>
       </c>
       <c r="H256">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I256">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="J256">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.35">
@@ -8734,22 +8737,22 @@
         <v>11</v>
       </c>
       <c r="E257" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F257" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G257" t="s">
         <v>25</v>
       </c>
       <c r="H257">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="I257">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="J257">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.35">
@@ -8766,22 +8769,22 @@
         <v>11</v>
       </c>
       <c r="E258" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F258" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G258" t="s">
         <v>24</v>
       </c>
       <c r="H258">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I258">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J258">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.35">
@@ -8798,22 +8801,22 @@
         <v>11</v>
       </c>
       <c r="E259" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F259" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G259" t="s">
         <v>25</v>
       </c>
       <c r="H259">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="I259">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J259">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.35">
@@ -8830,19 +8833,19 @@
         <v>11</v>
       </c>
       <c r="E260" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F260" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G260" t="s">
         <v>24</v>
       </c>
       <c r="H260">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I260">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J260">
         <v>0</v>
@@ -8862,19 +8865,19 @@
         <v>11</v>
       </c>
       <c r="E261" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F261" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G261" t="s">
         <v>25</v>
       </c>
       <c r="H261">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I261">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J261">
         <v>0</v>
@@ -8882,7 +8885,7 @@
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
-        <v>44426</v>
+        <v>44425</v>
       </c>
       <c r="B262">
         <v>2021</v>
@@ -8894,19 +8897,19 @@
         <v>11</v>
       </c>
       <c r="E262" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F262" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G262" t="s">
         <v>24</v>
       </c>
       <c r="H262">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I262">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J262">
         <v>0</v>
@@ -8914,7 +8917,7 @@
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
-        <v>44426</v>
+        <v>44425</v>
       </c>
       <c r="B263">
         <v>2021</v>
@@ -8926,19 +8929,19 @@
         <v>11</v>
       </c>
       <c r="E263" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F263" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G263" t="s">
         <v>25</v>
       </c>
       <c r="H263">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I263">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J263">
         <v>0</v>
@@ -8946,7 +8949,7 @@
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
-        <v>44427</v>
+        <v>44426</v>
       </c>
       <c r="B264">
         <v>2021</v>
@@ -8958,19 +8961,19 @@
         <v>11</v>
       </c>
       <c r="E264" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F264" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G264" t="s">
         <v>24</v>
       </c>
       <c r="H264">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I264">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J264">
         <v>0</v>
@@ -8978,7 +8981,7 @@
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
-        <v>44427</v>
+        <v>44426</v>
       </c>
       <c r="B265">
         <v>2021</v>
@@ -8990,19 +8993,19 @@
         <v>11</v>
       </c>
       <c r="E265" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F265" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G265" t="s">
         <v>25</v>
       </c>
       <c r="H265">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I265">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J265">
         <v>0</v>
@@ -9022,19 +9025,19 @@
         <v>11</v>
       </c>
       <c r="E266" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F266" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G266" t="s">
         <v>24</v>
       </c>
       <c r="H266">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I266">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="J266">
         <v>0</v>
@@ -9054,19 +9057,19 @@
         <v>11</v>
       </c>
       <c r="E267" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F267" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G267" t="s">
         <v>25</v>
       </c>
       <c r="H267">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="I267">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="J267">
         <v>0</v>
@@ -9086,10 +9089,10 @@
         <v>11</v>
       </c>
       <c r="E268" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F268" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G268" t="s">
         <v>24</v>
@@ -9098,7 +9101,7 @@
         <v>64</v>
       </c>
       <c r="I268">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="J268">
         <v>0</v>
@@ -9118,16 +9121,16 @@
         <v>11</v>
       </c>
       <c r="E269" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F269" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G269" t="s">
         <v>25</v>
       </c>
       <c r="H269">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="I269">
         <v>64</v>
@@ -9138,7 +9141,7 @@
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
-        <v>44428</v>
+        <v>44427</v>
       </c>
       <c r="B270">
         <v>2021</v>
@@ -9150,19 +9153,19 @@
         <v>11</v>
       </c>
       <c r="E270" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F270" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G270" t="s">
         <v>24</v>
       </c>
       <c r="H270">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="I270">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="J270">
         <v>0</v>
@@ -9170,7 +9173,7 @@
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
-        <v>44428</v>
+        <v>44427</v>
       </c>
       <c r="B271">
         <v>2021</v>
@@ -9182,19 +9185,19 @@
         <v>11</v>
       </c>
       <c r="E271" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F271" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G271" t="s">
         <v>25</v>
       </c>
       <c r="H271">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I271">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="J271">
         <v>0</v>
@@ -9214,19 +9217,19 @@
         <v>11</v>
       </c>
       <c r="E272" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F272" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G272" t="s">
         <v>24</v>
       </c>
       <c r="H272">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="I272">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J272">
         <v>0</v>
@@ -9246,19 +9249,19 @@
         <v>11</v>
       </c>
       <c r="E273" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F273" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G273" t="s">
         <v>25</v>
       </c>
       <c r="H273">
+        <v>81</v>
+      </c>
+      <c r="I273">
         <v>83</v>
-      </c>
-      <c r="I273">
-        <v>99</v>
       </c>
       <c r="J273">
         <v>0</v>
@@ -9266,7 +9269,7 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
-        <v>44429</v>
+        <v>44428</v>
       </c>
       <c r="B274">
         <v>2021</v>
@@ -9278,19 +9281,19 @@
         <v>11</v>
       </c>
       <c r="E274" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F274" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G274" t="s">
         <v>24</v>
       </c>
       <c r="H274">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="I274">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="J274">
         <v>0</v>
@@ -9298,7 +9301,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
-        <v>44429</v>
+        <v>44428</v>
       </c>
       <c r="B275">
         <v>2021</v>
@@ -9310,19 +9313,19 @@
         <v>11</v>
       </c>
       <c r="E275" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F275" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G275" t="s">
         <v>25</v>
       </c>
       <c r="H275">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="I275">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="J275">
         <v>0</v>
@@ -9342,19 +9345,19 @@
         <v>11</v>
       </c>
       <c r="E276" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F276" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G276" t="s">
         <v>24</v>
       </c>
       <c r="H276">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I276">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J276">
         <v>0</v>
@@ -9374,19 +9377,19 @@
         <v>11</v>
       </c>
       <c r="E277" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F277" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G277" t="s">
         <v>25</v>
       </c>
       <c r="H277">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="I277">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="J277">
         <v>0</v>
@@ -9394,7 +9397,7 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
-        <v>44430</v>
+        <v>44429</v>
       </c>
       <c r="B278">
         <v>2021</v>
@@ -9406,19 +9409,19 @@
         <v>11</v>
       </c>
       <c r="E278" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F278" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G278" t="s">
         <v>24</v>
       </c>
       <c r="H278">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="I278">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J278">
         <v>0</v>
@@ -9426,7 +9429,7 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
-        <v>44430</v>
+        <v>44429</v>
       </c>
       <c r="B279">
         <v>2021</v>
@@ -9438,19 +9441,19 @@
         <v>11</v>
       </c>
       <c r="E279" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F279" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G279" t="s">
         <v>25</v>
       </c>
       <c r="H279">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I279">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="J279">
         <v>0</v>
@@ -9470,19 +9473,19 @@
         <v>11</v>
       </c>
       <c r="E280" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F280" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G280" t="s">
         <v>24</v>
       </c>
       <c r="H280">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I280">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J280">
         <v>0</v>
@@ -9502,19 +9505,19 @@
         <v>11</v>
       </c>
       <c r="E281" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F281" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G281" t="s">
         <v>25</v>
       </c>
       <c r="H281">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I281">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J281">
         <v>0</v>
@@ -9522,7 +9525,7 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
-        <v>44432</v>
+        <v>44430</v>
       </c>
       <c r="B282">
         <v>2021</v>
@@ -9534,19 +9537,19 @@
         <v>11</v>
       </c>
       <c r="E282" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F282" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G282" t="s">
         <v>24</v>
       </c>
       <c r="H282">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I282">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J282">
         <v>0</v>
@@ -9554,7 +9557,7 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
-        <v>44432</v>
+        <v>44430</v>
       </c>
       <c r="B283">
         <v>2021</v>
@@ -9566,19 +9569,19 @@
         <v>11</v>
       </c>
       <c r="E283" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F283" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G283" t="s">
         <v>25</v>
       </c>
       <c r="H283">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I283">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J283">
         <v>0</v>
@@ -9598,19 +9601,19 @@
         <v>11</v>
       </c>
       <c r="E284" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F284" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G284" t="s">
         <v>24</v>
       </c>
       <c r="H284">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="I284">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J284">
         <v>0</v>
@@ -9630,19 +9633,19 @@
         <v>11</v>
       </c>
       <c r="E285" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F285" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G285" t="s">
         <v>25</v>
       </c>
       <c r="H285">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I285">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="J285">
         <v>0</v>
@@ -9662,16 +9665,16 @@
         <v>11</v>
       </c>
       <c r="E286" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F286" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G286" t="s">
         <v>24</v>
       </c>
       <c r="H286">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="I286">
         <v>76</v>
@@ -9694,10 +9697,10 @@
         <v>11</v>
       </c>
       <c r="E287" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F287" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G287" t="s">
         <v>25</v>
@@ -9706,7 +9709,7 @@
         <v>76</v>
       </c>
       <c r="I287">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J287">
         <v>0</v>
@@ -9726,19 +9729,19 @@
         <v>11</v>
       </c>
       <c r="E288" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F288" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G288" t="s">
         <v>24</v>
       </c>
       <c r="H288">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I288">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J288">
         <v>0</v>
@@ -9758,19 +9761,19 @@
         <v>11</v>
       </c>
       <c r="E289" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F289" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G289" t="s">
         <v>25</v>
       </c>
       <c r="H289">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I289">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J289">
         <v>0</v>
@@ -9778,7 +9781,7 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
-        <v>44433</v>
+        <v>44432</v>
       </c>
       <c r="B290">
         <v>2021</v>
@@ -9790,19 +9793,19 @@
         <v>11</v>
       </c>
       <c r="E290" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F290" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G290" t="s">
         <v>24</v>
       </c>
       <c r="H290">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="I290">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J290">
         <v>0</v>
@@ -9810,7 +9813,7 @@
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
-        <v>44433</v>
+        <v>44432</v>
       </c>
       <c r="B291">
         <v>2021</v>
@@ -9822,19 +9825,19 @@
         <v>11</v>
       </c>
       <c r="E291" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F291" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G291" t="s">
         <v>25</v>
       </c>
       <c r="H291">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I291">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="J291">
         <v>0</v>
@@ -9842,7 +9845,7 @@
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
-        <v>44434</v>
+        <v>44433</v>
       </c>
       <c r="B292">
         <v>2021</v>
@@ -9854,19 +9857,19 @@
         <v>11</v>
       </c>
       <c r="E292" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F292" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G292" t="s">
         <v>24</v>
       </c>
       <c r="H292">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="I292">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J292">
         <v>0</v>
@@ -9874,7 +9877,7 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
-        <v>44434</v>
+        <v>44433</v>
       </c>
       <c r="B293">
         <v>2021</v>
@@ -9886,19 +9889,19 @@
         <v>11</v>
       </c>
       <c r="E293" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F293" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G293" t="s">
         <v>25</v>
       </c>
       <c r="H293">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I293">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="J293">
         <v>0</v>
@@ -9918,19 +9921,19 @@
         <v>11</v>
       </c>
       <c r="E294" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F294" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G294" t="s">
         <v>24</v>
       </c>
       <c r="H294">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I294">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J294">
         <v>0</v>
@@ -9950,19 +9953,19 @@
         <v>11</v>
       </c>
       <c r="E295" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F295" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G295" t="s">
         <v>25</v>
       </c>
       <c r="H295">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I295">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J295">
         <v>0</v>
@@ -9982,19 +9985,19 @@
         <v>11</v>
       </c>
       <c r="E296" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F296" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G296" t="s">
         <v>24</v>
       </c>
       <c r="H296">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="I296">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J296">
         <v>0</v>
@@ -10014,19 +10017,19 @@
         <v>11</v>
       </c>
       <c r="E297" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F297" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G297" t="s">
         <v>25</v>
       </c>
       <c r="H297">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I297">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="J297">
         <v>0</v>
@@ -10034,7 +10037,7 @@
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
-        <v>44435</v>
+        <v>44434</v>
       </c>
       <c r="B298">
         <v>2021</v>
@@ -10046,19 +10049,19 @@
         <v>11</v>
       </c>
       <c r="E298" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F298" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G298" t="s">
         <v>24</v>
       </c>
       <c r="H298">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I298">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="J298">
         <v>0</v>
@@ -10066,7 +10069,7 @@
     </row>
     <row r="299" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
-        <v>44435</v>
+        <v>44434</v>
       </c>
       <c r="B299">
         <v>2021</v>
@@ -10078,19 +10081,19 @@
         <v>11</v>
       </c>
       <c r="E299" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F299" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G299" t="s">
         <v>25</v>
       </c>
       <c r="H299">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="I299">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J299">
         <v>0</v>
@@ -10110,19 +10113,19 @@
         <v>11</v>
       </c>
       <c r="E300" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F300" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G300" t="s">
         <v>24</v>
       </c>
       <c r="H300">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="I300">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="J300">
         <v>0</v>
@@ -10142,19 +10145,19 @@
         <v>11</v>
       </c>
       <c r="E301" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F301" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G301" t="s">
         <v>25</v>
       </c>
       <c r="H301">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I301">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J301">
         <v>0</v>
@@ -10162,7 +10165,7 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
-        <v>44436</v>
+        <v>44435</v>
       </c>
       <c r="B302">
         <v>2021</v>
@@ -10174,19 +10177,19 @@
         <v>11</v>
       </c>
       <c r="E302" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F302" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G302" t="s">
         <v>24</v>
       </c>
       <c r="H302">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="I302">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="J302">
         <v>0</v>
@@ -10194,7 +10197,7 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
-        <v>44436</v>
+        <v>44435</v>
       </c>
       <c r="B303">
         <v>2021</v>
@@ -10206,19 +10209,19 @@
         <v>11</v>
       </c>
       <c r="E303" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F303" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G303" t="s">
         <v>25</v>
       </c>
       <c r="H303">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I303">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="J303">
         <v>0</v>
@@ -10238,19 +10241,19 @@
         <v>11</v>
       </c>
       <c r="E304" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F304" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G304" t="s">
         <v>24</v>
       </c>
       <c r="H304">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="I304">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J304">
         <v>0</v>
@@ -10270,19 +10273,19 @@
         <v>11</v>
       </c>
       <c r="E305" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F305" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G305" t="s">
         <v>25</v>
       </c>
       <c r="H305">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I305">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="J305">
         <v>0</v>
@@ -10302,19 +10305,19 @@
         <v>11</v>
       </c>
       <c r="E306" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F306" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G306" t="s">
         <v>24</v>
       </c>
       <c r="H306">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="I306">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J306">
         <v>0</v>
@@ -10334,19 +10337,19 @@
         <v>11</v>
       </c>
       <c r="E307" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F307" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G307" t="s">
         <v>25</v>
       </c>
       <c r="H307">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I307">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J307">
         <v>0</v>
@@ -10354,7 +10357,7 @@
     </row>
     <row r="308" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
-        <v>44437</v>
+        <v>44436</v>
       </c>
       <c r="B308">
         <v>2021</v>
@@ -10366,19 +10369,19 @@
         <v>11</v>
       </c>
       <c r="E308" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F308" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G308" t="s">
         <v>24</v>
       </c>
       <c r="H308">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="I308">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J308">
         <v>0</v>
@@ -10386,7 +10389,7 @@
     </row>
     <row r="309" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
-        <v>44437</v>
+        <v>44436</v>
       </c>
       <c r="B309">
         <v>2021</v>
@@ -10398,19 +10401,19 @@
         <v>11</v>
       </c>
       <c r="E309" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F309" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G309" t="s">
         <v>25</v>
       </c>
       <c r="H309">
+        <v>76</v>
+      </c>
+      <c r="I309">
         <v>75</v>
-      </c>
-      <c r="I309">
-        <v>107</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -10418,7 +10421,7 @@
     </row>
     <row r="310" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
-        <v>44439</v>
+        <v>44437</v>
       </c>
       <c r="B310">
         <v>2021</v>
@@ -10430,19 +10433,19 @@
         <v>11</v>
       </c>
       <c r="E310" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F310" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G310" t="s">
         <v>24</v>
       </c>
       <c r="H310">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="I310">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J310">
         <v>0</v>
@@ -10450,7 +10453,7 @@
     </row>
     <row r="311" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
-        <v>44439</v>
+        <v>44437</v>
       </c>
       <c r="B311">
         <v>2021</v>
@@ -10462,19 +10465,19 @@
         <v>11</v>
       </c>
       <c r="E311" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F311" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G311" t="s">
         <v>25</v>
       </c>
       <c r="H311">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I311">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="J311">
         <v>0</v>
@@ -10494,16 +10497,16 @@
         <v>11</v>
       </c>
       <c r="E312" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F312" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G312" t="s">
         <v>24</v>
       </c>
       <c r="H312">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I312">
         <v>74</v>
@@ -10526,10 +10529,10 @@
         <v>11</v>
       </c>
       <c r="E313" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F313" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G313" t="s">
         <v>25</v>
@@ -10538,7 +10541,7 @@
         <v>74</v>
       </c>
       <c r="I313">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="J313">
         <v>0</v>
@@ -10558,19 +10561,19 @@
         <v>11</v>
       </c>
       <c r="E314" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F314" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G314" t="s">
         <v>24</v>
       </c>
       <c r="H314">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="I314">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="J314">
         <v>0</v>
@@ -10590,19 +10593,19 @@
         <v>11</v>
       </c>
       <c r="E315" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F315" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G315" t="s">
         <v>25</v>
       </c>
       <c r="H315">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="I315">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="J315">
         <v>0</v>
@@ -10622,19 +10625,19 @@
         <v>11</v>
       </c>
       <c r="E316" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F316" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G316" t="s">
         <v>24</v>
       </c>
       <c r="H316">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I316">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="J316">
         <v>0</v>
@@ -10654,19 +10657,19 @@
         <v>11</v>
       </c>
       <c r="E317" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F317" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G317" t="s">
         <v>25</v>
       </c>
       <c r="H317">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="I317">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J317">
         <v>0</v>
@@ -10674,7 +10677,7 @@
     </row>
     <row r="318" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
-        <v>44441</v>
+        <v>44439</v>
       </c>
       <c r="B318">
         <v>2021</v>
@@ -10686,19 +10689,19 @@
         <v>11</v>
       </c>
       <c r="E318" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F318" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G318" t="s">
         <v>24</v>
       </c>
       <c r="H318">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="I318">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J318">
         <v>0</v>
@@ -10706,7 +10709,7 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
-        <v>44441</v>
+        <v>44439</v>
       </c>
       <c r="B319">
         <v>2021</v>
@@ -10718,19 +10721,19 @@
         <v>11</v>
       </c>
       <c r="E319" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F319" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G319" t="s">
         <v>25</v>
       </c>
       <c r="H319">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I319">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="J319">
         <v>0</v>
@@ -10750,19 +10753,19 @@
         <v>11</v>
       </c>
       <c r="E320" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F320" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G320" t="s">
         <v>24</v>
       </c>
       <c r="H320">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="I320">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="J320">
         <v>0</v>
@@ -10782,19 +10785,19 @@
         <v>11</v>
       </c>
       <c r="E321" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F321" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G321" t="s">
         <v>25</v>
       </c>
       <c r="H321">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="I321">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="J321">
         <v>0</v>
@@ -10814,19 +10817,19 @@
         <v>11</v>
       </c>
       <c r="E322" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F322" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G322" t="s">
         <v>24</v>
       </c>
       <c r="H322">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="I322">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="J322">
         <v>0</v>
@@ -10846,19 +10849,19 @@
         <v>11</v>
       </c>
       <c r="E323" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F323" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G323" t="s">
         <v>25</v>
       </c>
       <c r="H323">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="I323">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="J323">
         <v>0</v>
@@ -10878,19 +10881,19 @@
         <v>11</v>
       </c>
       <c r="E324" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F324" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G324" t="s">
         <v>24</v>
       </c>
       <c r="H324">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="I324">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J324">
         <v>0</v>
@@ -10910,19 +10913,19 @@
         <v>11</v>
       </c>
       <c r="E325" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F325" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G325" t="s">
         <v>25</v>
       </c>
       <c r="H325">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="I325">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="J325">
         <v>0</v>
@@ -10930,7 +10933,7 @@
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
-        <v>44443</v>
+        <v>44441</v>
       </c>
       <c r="B326">
         <v>2021</v>
@@ -10942,19 +10945,19 @@
         <v>11</v>
       </c>
       <c r="E326" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F326" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G326" t="s">
         <v>24</v>
       </c>
       <c r="H326">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="I326">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="J326">
         <v>0</v>
@@ -10962,7 +10965,7 @@
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
-        <v>44443</v>
+        <v>44441</v>
       </c>
       <c r="B327">
         <v>2021</v>
@@ -10974,19 +10977,19 @@
         <v>11</v>
       </c>
       <c r="E327" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F327" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G327" t="s">
         <v>25</v>
       </c>
       <c r="H327">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="I327">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J327">
         <v>0</v>
@@ -11006,19 +11009,19 @@
         <v>11</v>
       </c>
       <c r="E328" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F328" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G328" t="s">
         <v>24</v>
       </c>
       <c r="H328">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="I328">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="J328">
         <v>0</v>
@@ -11038,19 +11041,19 @@
         <v>11</v>
       </c>
       <c r="E329" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F329" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G329" t="s">
         <v>25</v>
       </c>
       <c r="H329">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="I329">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J329">
         <v>0</v>
@@ -11058,7 +11061,7 @@
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
-        <v>44444</v>
+        <v>44443</v>
       </c>
       <c r="B330">
         <v>2021</v>
@@ -11070,19 +11073,19 @@
         <v>11</v>
       </c>
       <c r="E330" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F330" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G330" t="s">
         <v>24</v>
       </c>
       <c r="H330">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I330">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J330">
         <v>0</v>
@@ -11090,7 +11093,7 @@
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
-        <v>44444</v>
+        <v>44443</v>
       </c>
       <c r="B331">
         <v>2021</v>
@@ -11102,19 +11105,19 @@
         <v>11</v>
       </c>
       <c r="E331" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F331" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G331" t="s">
         <v>25</v>
       </c>
       <c r="H331">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I331">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="J331">
         <v>0</v>
@@ -11134,19 +11137,19 @@
         <v>11</v>
       </c>
       <c r="E332" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F332" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G332" t="s">
         <v>24</v>
       </c>
       <c r="H332">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="I332">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="J332">
         <v>0</v>
@@ -11166,19 +11169,19 @@
         <v>11</v>
       </c>
       <c r="E333" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F333" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G333" t="s">
         <v>25</v>
       </c>
       <c r="H333">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="I333">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="J333">
         <v>0</v>
@@ -11186,7 +11189,7 @@
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
-        <v>44445</v>
+        <v>44444</v>
       </c>
       <c r="B334">
         <v>2021</v>
@@ -11198,19 +11201,19 @@
         <v>11</v>
       </c>
       <c r="E334" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F334" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G334" t="s">
         <v>24</v>
       </c>
       <c r="H334">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="I334">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="J334">
         <v>0</v>
@@ -11218,7 +11221,7 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
-        <v>44445</v>
+        <v>44444</v>
       </c>
       <c r="B335">
         <v>2021</v>
@@ -11230,19 +11233,19 @@
         <v>11</v>
       </c>
       <c r="E335" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F335" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G335" t="s">
         <v>25</v>
       </c>
       <c r="H335">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="I335">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="J335">
         <v>0</v>
@@ -11250,7 +11253,7 @@
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
-        <v>44446</v>
+        <v>44445</v>
       </c>
       <c r="B336">
         <v>2021</v>
@@ -11262,19 +11265,19 @@
         <v>11</v>
       </c>
       <c r="E336" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F336" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G336" t="s">
         <v>24</v>
       </c>
       <c r="H336">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I336">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="J336">
         <v>0</v>
@@ -11282,7 +11285,7 @@
     </row>
     <row r="337" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
-        <v>44446</v>
+        <v>44445</v>
       </c>
       <c r="B337">
         <v>2021</v>
@@ -11294,19 +11297,19 @@
         <v>11</v>
       </c>
       <c r="E337" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F337" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G337" t="s">
         <v>25</v>
       </c>
       <c r="H337">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="I337">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J337">
         <v>0</v>
@@ -11326,19 +11329,19 @@
         <v>11</v>
       </c>
       <c r="E338" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F338" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G338" t="s">
         <v>24</v>
       </c>
       <c r="H338">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I338">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="J338">
         <v>0</v>
@@ -11358,19 +11361,19 @@
         <v>11</v>
       </c>
       <c r="E339" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F339" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G339" t="s">
         <v>25</v>
       </c>
       <c r="H339">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="I339">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="J339">
         <v>0</v>
@@ -11378,7 +11381,7 @@
     </row>
     <row r="340" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
-        <v>44447</v>
+        <v>44446</v>
       </c>
       <c r="B340">
         <v>2021</v>
@@ -11390,19 +11393,19 @@
         <v>11</v>
       </c>
       <c r="E340" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F340" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G340" t="s">
         <v>24</v>
       </c>
       <c r="H340">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I340">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="J340">
         <v>0</v>
@@ -11410,7 +11413,7 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
-        <v>44447</v>
+        <v>44446</v>
       </c>
       <c r="B341">
         <v>2021</v>
@@ -11422,19 +11425,19 @@
         <v>11</v>
       </c>
       <c r="E341" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F341" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G341" t="s">
         <v>25</v>
       </c>
       <c r="H341">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="I341">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J341">
         <v>0</v>
@@ -11454,19 +11457,19 @@
         <v>11</v>
       </c>
       <c r="E342" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F342" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G342" t="s">
         <v>24</v>
       </c>
       <c r="H342">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="I342">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="J342">
         <v>0</v>
@@ -11486,19 +11489,19 @@
         <v>11</v>
       </c>
       <c r="E343" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F343" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G343" t="s">
         <v>25</v>
       </c>
       <c r="H343">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="I343">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="J343">
         <v>0</v>
@@ -11506,7 +11509,7 @@
     </row>
     <row r="344" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
-        <v>44448</v>
+        <v>44447</v>
       </c>
       <c r="B344">
         <v>2021</v>
@@ -11518,19 +11521,19 @@
         <v>11</v>
       </c>
       <c r="E344" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F344" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G344" t="s">
         <v>24</v>
       </c>
       <c r="H344">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I344">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="J344">
         <v>0</v>
@@ -11538,7 +11541,7 @@
     </row>
     <row r="345" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
-        <v>44448</v>
+        <v>44447</v>
       </c>
       <c r="B345">
         <v>2021</v>
@@ -11550,19 +11553,19 @@
         <v>11</v>
       </c>
       <c r="E345" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="F345" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G345" t="s">
         <v>25</v>
       </c>
       <c r="H345">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="I345">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J345">
         <v>0</v>
@@ -11570,7 +11573,7 @@
     </row>
     <row r="346" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
-        <v>44449</v>
+        <v>44448</v>
       </c>
       <c r="B346">
         <v>2021</v>
@@ -11582,19 +11585,19 @@
         <v>11</v>
       </c>
       <c r="E346" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F346" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G346" t="s">
         <v>24</v>
       </c>
       <c r="H346">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I346">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="J346">
         <v>0</v>
@@ -11602,7 +11605,7 @@
     </row>
     <row r="347" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
-        <v>44449</v>
+        <v>44448</v>
       </c>
       <c r="B347">
         <v>2021</v>
@@ -11614,19 +11617,19 @@
         <v>11</v>
       </c>
       <c r="E347" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F347" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G347" t="s">
         <v>25</v>
       </c>
       <c r="H347">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="I347">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J347">
         <v>0</v>
@@ -11646,19 +11649,19 @@
         <v>11</v>
       </c>
       <c r="E348" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F348" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G348" t="s">
         <v>24</v>
       </c>
       <c r="H348">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I348">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J348">
         <v>0</v>
@@ -11678,19 +11681,19 @@
         <v>11</v>
       </c>
       <c r="E349" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F349" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G349" t="s">
         <v>25</v>
       </c>
       <c r="H349">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I349">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J349">
         <v>0</v>
@@ -11698,7 +11701,7 @@
     </row>
     <row r="350" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
-        <v>44450</v>
+        <v>44449</v>
       </c>
       <c r="B350">
         <v>2021</v>
@@ -11710,19 +11713,19 @@
         <v>11</v>
       </c>
       <c r="E350" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F350" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G350" t="s">
         <v>24</v>
       </c>
       <c r="H350">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I350">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J350">
         <v>0</v>
@@ -11730,7 +11733,7 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
-        <v>44450</v>
+        <v>44449</v>
       </c>
       <c r="B351">
         <v>2021</v>
@@ -11742,19 +11745,19 @@
         <v>11</v>
       </c>
       <c r="E351" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F351" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G351" t="s">
         <v>25</v>
       </c>
       <c r="H351">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I351">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J351">
         <v>0</v>
@@ -11774,10 +11777,10 @@
         <v>11</v>
       </c>
       <c r="E352" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F352" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G352" t="s">
         <v>24</v>
@@ -11786,7 +11789,7 @@
         <v>76</v>
       </c>
       <c r="I352">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="J352">
         <v>0</v>
@@ -11806,16 +11809,16 @@
         <v>11</v>
       </c>
       <c r="E353" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F353" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G353" t="s">
         <v>25</v>
       </c>
       <c r="H353">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="I353">
         <v>76</v>
@@ -11826,7 +11829,7 @@
     </row>
     <row r="354" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
-        <v>44451</v>
+        <v>44450</v>
       </c>
       <c r="B354">
         <v>2021</v>
@@ -11838,19 +11841,19 @@
         <v>11</v>
       </c>
       <c r="E354" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F354" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G354" t="s">
         <v>24</v>
       </c>
       <c r="H354">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I354">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J354">
         <v>0</v>
@@ -11858,7 +11861,7 @@
     </row>
     <row r="355" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
-        <v>44451</v>
+        <v>44450</v>
       </c>
       <c r="B355">
         <v>2021</v>
@@ -11870,19 +11873,19 @@
         <v>11</v>
       </c>
       <c r="E355" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F355" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G355" t="s">
         <v>25</v>
       </c>
       <c r="H355">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="I355">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J355">
         <v>0</v>
@@ -11902,19 +11905,19 @@
         <v>11</v>
       </c>
       <c r="E356" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F356" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G356" t="s">
         <v>24</v>
       </c>
       <c r="H356">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="I356">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="J356">
         <v>0</v>
@@ -11934,19 +11937,19 @@
         <v>11</v>
       </c>
       <c r="E357" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F357" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G357" t="s">
         <v>25</v>
       </c>
       <c r="H357">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="I357">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="J357">
         <v>0</v>
@@ -11966,19 +11969,19 @@
         <v>11</v>
       </c>
       <c r="E358" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F358" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G358" t="s">
         <v>24</v>
       </c>
       <c r="H358">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="I358">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J358">
         <v>0</v>
@@ -11998,19 +12001,19 @@
         <v>11</v>
       </c>
       <c r="E359" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F359" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G359" t="s">
         <v>25</v>
       </c>
       <c r="H359">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="I359">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="J359">
         <v>0</v>
@@ -12018,7 +12021,7 @@
     </row>
     <row r="360" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
-        <v>44452</v>
+        <v>44451</v>
       </c>
       <c r="B360">
         <v>2021</v>
@@ -12030,19 +12033,19 @@
         <v>11</v>
       </c>
       <c r="E360" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F360" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G360" t="s">
         <v>24</v>
       </c>
       <c r="H360">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I360">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J360">
         <v>0</v>
@@ -12050,7 +12053,7 @@
     </row>
     <row r="361" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
-        <v>44452</v>
+        <v>44451</v>
       </c>
       <c r="B361">
         <v>2021</v>
@@ -12062,19 +12065,19 @@
         <v>11</v>
       </c>
       <c r="E361" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F361" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G361" t="s">
         <v>25</v>
       </c>
       <c r="H361">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I361">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J361">
         <v>0</v>
@@ -12082,7 +12085,7 @@
     </row>
     <row r="362" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
-        <v>44453</v>
+        <v>44452</v>
       </c>
       <c r="B362">
         <v>2021</v>
@@ -12094,16 +12097,16 @@
         <v>11</v>
       </c>
       <c r="E362" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F362" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G362" t="s">
         <v>24</v>
       </c>
       <c r="H362">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I362">
         <v>85</v>
@@ -12114,7 +12117,7 @@
     </row>
     <row r="363" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
-        <v>44453</v>
+        <v>44452</v>
       </c>
       <c r="B363">
         <v>2021</v>
@@ -12126,10 +12129,10 @@
         <v>11</v>
       </c>
       <c r="E363" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F363" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G363" t="s">
         <v>25</v>
@@ -12138,7 +12141,7 @@
         <v>85</v>
       </c>
       <c r="I363">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="J363">
         <v>0</v>
@@ -12146,7 +12149,7 @@
     </row>
     <row r="364" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
-        <v>44454</v>
+        <v>44453</v>
       </c>
       <c r="B364">
         <v>2021</v>
@@ -12158,19 +12161,19 @@
         <v>11</v>
       </c>
       <c r="E364" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F364" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G364" t="s">
         <v>24</v>
       </c>
       <c r="H364">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I364">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="J364">
         <v>0</v>
@@ -12178,7 +12181,7 @@
     </row>
     <row r="365" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
-        <v>44454</v>
+        <v>44453</v>
       </c>
       <c r="B365">
         <v>2021</v>
@@ -12190,19 +12193,19 @@
         <v>11</v>
       </c>
       <c r="E365" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F365" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G365" t="s">
         <v>25</v>
       </c>
       <c r="H365">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="I365">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="J365">
         <v>0</v>
@@ -12210,7 +12213,7 @@
     </row>
     <row r="366" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
-        <v>44455</v>
+        <v>44454</v>
       </c>
       <c r="B366">
         <v>2021</v>
@@ -12222,19 +12225,19 @@
         <v>11</v>
       </c>
       <c r="E366" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F366" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G366" t="s">
         <v>24</v>
       </c>
       <c r="H366">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I366">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="J366">
         <v>0</v>
@@ -12242,7 +12245,7 @@
     </row>
     <row r="367" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
-        <v>44455</v>
+        <v>44454</v>
       </c>
       <c r="B367">
         <v>2021</v>
@@ -12254,19 +12257,19 @@
         <v>11</v>
       </c>
       <c r="E367" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F367" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G367" t="s">
         <v>25</v>
       </c>
       <c r="H367">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="I367">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J367">
         <v>0</v>
@@ -12274,7 +12277,7 @@
     </row>
     <row r="368" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
-        <v>44456</v>
+        <v>44455</v>
       </c>
       <c r="B368">
         <v>2021</v>
@@ -12286,19 +12289,19 @@
         <v>11</v>
       </c>
       <c r="E368" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F368" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G368" t="s">
         <v>24</v>
       </c>
       <c r="H368">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="I368">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J368">
         <v>0</v>
@@ -12306,7 +12309,7 @@
     </row>
     <row r="369" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
-        <v>44456</v>
+        <v>44455</v>
       </c>
       <c r="B369">
         <v>2021</v>
@@ -12318,19 +12321,19 @@
         <v>11</v>
       </c>
       <c r="E369" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F369" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G369" t="s">
         <v>25</v>
       </c>
       <c r="H369">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I369">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="J369">
         <v>0</v>
@@ -12350,19 +12353,19 @@
         <v>11</v>
       </c>
       <c r="E370" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F370" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G370" t="s">
         <v>24</v>
       </c>
       <c r="H370">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="I370">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J370">
         <v>0</v>
@@ -12382,19 +12385,19 @@
         <v>11</v>
       </c>
       <c r="E371" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F371" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G371" t="s">
         <v>25</v>
       </c>
       <c r="H371">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I371">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="J371">
         <v>0</v>
@@ -12414,19 +12417,19 @@
         <v>11</v>
       </c>
       <c r="E372" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F372" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G372" t="s">
         <v>24</v>
       </c>
       <c r="H372">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I372">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="J372">
         <v>0</v>
@@ -12446,19 +12449,19 @@
         <v>11</v>
       </c>
       <c r="E373" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F373" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G373" t="s">
         <v>25</v>
       </c>
       <c r="H373">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="I373">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J373">
         <v>0</v>
@@ -12478,19 +12481,19 @@
         <v>11</v>
       </c>
       <c r="E374" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F374" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G374" t="s">
         <v>24</v>
       </c>
       <c r="H374">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I374">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="J374">
         <v>0</v>
@@ -12510,19 +12513,19 @@
         <v>11</v>
       </c>
       <c r="E375" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F375" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G375" t="s">
         <v>25</v>
       </c>
       <c r="H375">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I375">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J375">
         <v>0</v>
@@ -12530,7 +12533,7 @@
     </row>
     <row r="376" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
-        <v>44458</v>
+        <v>44456</v>
       </c>
       <c r="B376">
         <v>2021</v>
@@ -12542,19 +12545,19 @@
         <v>11</v>
       </c>
       <c r="E376" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F376" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G376" t="s">
         <v>24</v>
       </c>
       <c r="H376">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="I376">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J376">
         <v>0</v>
@@ -12562,7 +12565,7 @@
     </row>
     <row r="377" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
-        <v>44458</v>
+        <v>44456</v>
       </c>
       <c r="B377">
         <v>2021</v>
@@ -12574,19 +12577,19 @@
         <v>11</v>
       </c>
       <c r="E377" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F377" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G377" t="s">
         <v>25</v>
       </c>
       <c r="H377">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I377">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J377">
         <v>0</v>
@@ -12606,19 +12609,19 @@
         <v>11</v>
       </c>
       <c r="E378" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F378" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G378" t="s">
         <v>24</v>
       </c>
       <c r="H378">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="I378">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="J378">
         <v>0</v>
@@ -12638,19 +12641,19 @@
         <v>11</v>
       </c>
       <c r="E379" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F379" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G379" t="s">
         <v>25</v>
       </c>
       <c r="H379">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="I379">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="J379">
         <v>0</v>
@@ -12670,19 +12673,19 @@
         <v>11</v>
       </c>
       <c r="E380" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F380" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G380" t="s">
         <v>24</v>
       </c>
       <c r="H380">
+        <v>64</v>
+      </c>
+      <c r="I380">
         <v>84</v>
-      </c>
-      <c r="I380">
-        <v>87</v>
       </c>
       <c r="J380">
         <v>0</v>
@@ -12702,19 +12705,19 @@
         <v>11</v>
       </c>
       <c r="E381" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F381" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G381" t="s">
         <v>25</v>
       </c>
       <c r="H381">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I381">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="J381">
         <v>0</v>
@@ -12734,10 +12737,10 @@
         <v>11</v>
       </c>
       <c r="E382" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F382" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G382" t="s">
         <v>24</v>
@@ -12746,7 +12749,7 @@
         <v>84</v>
       </c>
       <c r="I382">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J382">
         <v>0</v>
@@ -12766,16 +12769,16 @@
         <v>11</v>
       </c>
       <c r="E383" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F383" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G383" t="s">
         <v>25</v>
       </c>
       <c r="H383">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="I383">
         <v>84</v>
@@ -12798,19 +12801,19 @@
         <v>11</v>
       </c>
       <c r="E384" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F384" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G384" t="s">
         <v>24</v>
       </c>
       <c r="H384">
+        <v>84</v>
+      </c>
+      <c r="I384">
         <v>83</v>
-      </c>
-      <c r="I384">
-        <v>77</v>
       </c>
       <c r="J384">
         <v>0</v>
@@ -12830,19 +12833,19 @@
         <v>11</v>
       </c>
       <c r="E385" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F385" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G385" t="s">
         <v>25</v>
       </c>
       <c r="H385">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I385">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J385">
         <v>0</v>
@@ -12850,31 +12853,31 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
-        <v>44462</v>
+        <v>44458</v>
       </c>
       <c r="B386">
         <v>2021</v>
       </c>
       <c r="C386" t="s">
-        <v>26</v>
-      </c>
-      <c r="D386">
-        <v>0.5</v>
+        <v>10</v>
+      </c>
+      <c r="D386" t="s">
+        <v>11</v>
       </c>
       <c r="E386" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F386" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G386" t="s">
         <v>24</v>
       </c>
       <c r="H386">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="I386">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="J386">
         <v>0</v>
@@ -12882,31 +12885,31 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
-        <v>44462</v>
+        <v>44458</v>
       </c>
       <c r="B387">
         <v>2021</v>
       </c>
       <c r="C387" t="s">
-        <v>26</v>
-      </c>
-      <c r="D387">
-        <v>0.5</v>
+        <v>10</v>
+      </c>
+      <c r="D387" t="s">
+        <v>11</v>
       </c>
       <c r="E387" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F387" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G387" t="s">
         <v>25</v>
       </c>
       <c r="H387">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I387">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="J387">
         <v>0</v>
@@ -12926,19 +12929,19 @@
         <v>0.5</v>
       </c>
       <c r="E388" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F388" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G388" t="s">
         <v>24</v>
       </c>
       <c r="H388">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="I388">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J388">
         <v>0</v>
@@ -12958,19 +12961,19 @@
         <v>0.5</v>
       </c>
       <c r="E389" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F389" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G389" t="s">
         <v>25</v>
       </c>
       <c r="H389">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I389">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="J389">
         <v>0</v>
@@ -12978,7 +12981,7 @@
     </row>
     <row r="390" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
-        <v>44465</v>
+        <v>44462</v>
       </c>
       <c r="B390">
         <v>2021</v>
@@ -12987,22 +12990,22 @@
         <v>26</v>
       </c>
       <c r="D390">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E390" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F390" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G390" t="s">
         <v>24</v>
       </c>
       <c r="H390">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I390">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="J390">
         <v>0</v>
@@ -13010,7 +13013,7 @@
     </row>
     <row r="391" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
-        <v>44465</v>
+        <v>44462</v>
       </c>
       <c r="B391">
         <v>2021</v>
@@ -13019,22 +13022,22 @@
         <v>26</v>
       </c>
       <c r="D391">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E391" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F391" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G391" t="s">
         <v>25</v>
       </c>
       <c r="H391">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I391">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="J391">
         <v>0</v>
@@ -13054,22 +13057,22 @@
         <v>1</v>
       </c>
       <c r="E392" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F392" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G392" t="s">
         <v>24</v>
       </c>
       <c r="H392">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I392">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J392">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393" spans="1:10" x14ac:dyDescent="0.35">
@@ -13086,27 +13089,27 @@
         <v>1</v>
       </c>
       <c r="E393" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F393" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G393" t="s">
         <v>25</v>
       </c>
       <c r="H393">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I393">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J393">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="394" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
-        <v>44467</v>
+        <v>44465</v>
       </c>
       <c r="B394">
         <v>2021</v>
@@ -13115,22 +13118,22 @@
         <v>26</v>
       </c>
       <c r="D394">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E394" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F394" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G394" t="s">
         <v>24</v>
       </c>
       <c r="H394">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="I394">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J394">
         <v>1</v>
@@ -13138,7 +13141,7 @@
     </row>
     <row r="395" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
-        <v>44467</v>
+        <v>44465</v>
       </c>
       <c r="B395">
         <v>2021</v>
@@ -13147,22 +13150,22 @@
         <v>26</v>
       </c>
       <c r="D395">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E395" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F395" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G395" t="s">
         <v>25</v>
       </c>
       <c r="H395">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="I395">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="J395">
         <v>1</v>
@@ -13182,22 +13185,22 @@
         <v>2</v>
       </c>
       <c r="E396" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F396" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G396" t="s">
         <v>24</v>
       </c>
       <c r="H396">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="I396">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J396">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397" spans="1:10" x14ac:dyDescent="0.35">
@@ -13214,27 +13217,27 @@
         <v>2</v>
       </c>
       <c r="E397" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F397" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G397" t="s">
         <v>25</v>
       </c>
       <c r="H397">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I397">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="J397">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
-        <v>44469</v>
+        <v>44467</v>
       </c>
       <c r="B398">
         <v>2021</v>
@@ -13246,19 +13249,19 @@
         <v>2</v>
       </c>
       <c r="E398" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F398" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G398" t="s">
         <v>24</v>
       </c>
       <c r="H398">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="I398">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="J398">
         <v>0</v>
@@ -13266,7 +13269,7 @@
     </row>
     <row r="399" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
-        <v>44469</v>
+        <v>44467</v>
       </c>
       <c r="B399">
         <v>2021</v>
@@ -13278,19 +13281,19 @@
         <v>2</v>
       </c>
       <c r="E399" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F399" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G399" t="s">
         <v>25</v>
       </c>
       <c r="H399">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="I399">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="J399">
         <v>0</v>
@@ -13310,19 +13313,19 @@
         <v>2</v>
       </c>
       <c r="E400" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F400" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G400" t="s">
         <v>24</v>
       </c>
       <c r="H400">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="I400">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J400">
         <v>0</v>
@@ -13342,19 +13345,19 @@
         <v>2</v>
       </c>
       <c r="E401" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F401" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G401" t="s">
         <v>25</v>
       </c>
       <c r="H401">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I401">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="J401">
         <v>0</v>
@@ -13362,7 +13365,7 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A402" s="1">
-        <v>44472</v>
+        <v>44469</v>
       </c>
       <c r="B402">
         <v>2021</v>
@@ -13374,19 +13377,19 @@
         <v>2</v>
       </c>
       <c r="E402" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F402" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G402" t="s">
         <v>24</v>
       </c>
       <c r="H402">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="I402">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J402">
         <v>0</v>
@@ -13394,7 +13397,7 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A403" s="1">
-        <v>44472</v>
+        <v>44469</v>
       </c>
       <c r="B403">
         <v>2021</v>
@@ -13406,19 +13409,19 @@
         <v>2</v>
       </c>
       <c r="E403" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F403" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G403" t="s">
         <v>25</v>
       </c>
       <c r="H403">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I403">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="J403">
         <v>0</v>
@@ -13438,19 +13441,19 @@
         <v>2</v>
       </c>
       <c r="E404" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F404" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G404" t="s">
         <v>24</v>
       </c>
       <c r="H404">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="I404">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J404">
         <v>0</v>
@@ -13470,19 +13473,19 @@
         <v>2</v>
       </c>
       <c r="E405" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F405" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G405" t="s">
         <v>25</v>
       </c>
       <c r="H405">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I405">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="J405">
         <v>0</v>
@@ -13490,7 +13493,7 @@
     </row>
     <row r="406" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
-        <v>44475</v>
+        <v>44472</v>
       </c>
       <c r="B406">
         <v>2021</v>
@@ -13502,19 +13505,19 @@
         <v>2</v>
       </c>
       <c r="E406" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F406" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G406" t="s">
         <v>24</v>
       </c>
       <c r="H406">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="I406">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J406">
         <v>0</v>
@@ -13522,7 +13525,7 @@
     </row>
     <row r="407" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
-        <v>44475</v>
+        <v>44472</v>
       </c>
       <c r="B407">
         <v>2021</v>
@@ -13534,19 +13537,19 @@
         <v>2</v>
       </c>
       <c r="E407" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F407" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G407" t="s">
         <v>25</v>
       </c>
       <c r="H407">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I407">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="J407">
         <v>0</v>
@@ -13566,19 +13569,19 @@
         <v>2</v>
       </c>
       <c r="E408" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F408" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G408" t="s">
         <v>24</v>
       </c>
       <c r="H408">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="I408">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J408">
         <v>0</v>
@@ -13598,19 +13601,19 @@
         <v>2</v>
       </c>
       <c r="E409" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F409" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G409" t="s">
         <v>25</v>
       </c>
       <c r="H409">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I409">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="J409">
         <v>0</v>
@@ -13618,7 +13621,7 @@
     </row>
     <row r="410" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
-        <v>44477</v>
+        <v>44475</v>
       </c>
       <c r="B410">
         <v>2021</v>
@@ -13630,19 +13633,19 @@
         <v>2</v>
       </c>
       <c r="E410" t="s">
+        <v>23</v>
+      </c>
+      <c r="F410" t="s">
         <v>14</v>
       </c>
-      <c r="F410" t="s">
-        <v>23</v>
-      </c>
       <c r="G410" t="s">
         <v>24</v>
       </c>
       <c r="H410">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I410">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="J410">
         <v>0</v>
@@ -13650,7 +13653,7 @@
     </row>
     <row r="411" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
-        <v>44477</v>
+        <v>44475</v>
       </c>
       <c r="B411">
         <v>2021</v>
@@ -13662,19 +13665,19 @@
         <v>2</v>
       </c>
       <c r="E411" t="s">
+        <v>14</v>
+      </c>
+      <c r="F411" t="s">
         <v>23</v>
       </c>
-      <c r="F411" t="s">
-        <v>14</v>
-      </c>
       <c r="G411" t="s">
         <v>25</v>
       </c>
       <c r="H411">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I411">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J411">
         <v>0</v>
@@ -13682,7 +13685,7 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
-        <v>44479</v>
+        <v>44477</v>
       </c>
       <c r="B412">
         <v>2021</v>
@@ -13691,22 +13694,22 @@
         <v>26</v>
       </c>
       <c r="D412">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E412" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F412" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G412" t="s">
         <v>24</v>
       </c>
       <c r="H412">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I412">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J412">
         <v>0</v>
@@ -13714,7 +13717,7 @@
     </row>
     <row r="413" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
-        <v>44479</v>
+        <v>44477</v>
       </c>
       <c r="B413">
         <v>2021</v>
@@ -13723,22 +13726,22 @@
         <v>26</v>
       </c>
       <c r="D413">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E413" t="s">
+        <v>23</v>
+      </c>
+      <c r="F413" t="s">
         <v>14</v>
       </c>
-      <c r="F413" t="s">
-        <v>20</v>
-      </c>
       <c r="G413" t="s">
         <v>25</v>
       </c>
       <c r="H413">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="I413">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="J413">
         <v>0</v>
@@ -13746,7 +13749,7 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
-        <v>44482</v>
+        <v>44479</v>
       </c>
       <c r="B414">
         <v>2021</v>
@@ -13767,18 +13770,18 @@
         <v>24</v>
       </c>
       <c r="H414">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I414">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="J414">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
-        <v>44482</v>
+        <v>44479</v>
       </c>
       <c r="B415">
         <v>2021</v>
@@ -13799,18 +13802,18 @@
         <v>25</v>
       </c>
       <c r="H415">
+        <v>77</v>
+      </c>
+      <c r="I415">
         <v>91</v>
       </c>
-      <c r="I415">
-        <v>86</v>
-      </c>
       <c r="J415">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A416" s="1">
-        <v>44484</v>
+        <v>44482</v>
       </c>
       <c r="B416">
         <v>2021</v>
@@ -13822,27 +13825,27 @@
         <v>3</v>
       </c>
       <c r="E416" t="s">
+        <v>20</v>
+      </c>
+      <c r="F416" t="s">
         <v>14</v>
       </c>
-      <c r="F416" t="s">
-        <v>20</v>
-      </c>
       <c r="G416" t="s">
         <v>24</v>
       </c>
       <c r="H416">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="I416">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J416">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A417" s="1">
-        <v>44484</v>
+        <v>44482</v>
       </c>
       <c r="B417">
         <v>2021</v>
@@ -13854,27 +13857,27 @@
         <v>3</v>
       </c>
       <c r="E417" t="s">
+        <v>14</v>
+      </c>
+      <c r="F417" t="s">
         <v>20</v>
       </c>
-      <c r="F417" t="s">
-        <v>14</v>
-      </c>
       <c r="G417" t="s">
         <v>25</v>
       </c>
       <c r="H417">
+        <v>91</v>
+      </c>
+      <c r="I417">
         <v>86</v>
       </c>
-      <c r="I417">
-        <v>50</v>
-      </c>
       <c r="J417">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="418" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
-        <v>44486</v>
+        <v>44484</v>
       </c>
       <c r="B418">
         <v>2021</v>
@@ -13895,10 +13898,10 @@
         <v>24</v>
       </c>
       <c r="H418">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="I418">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J418">
         <v>0</v>
@@ -13906,7 +13909,7 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
-        <v>44486</v>
+        <v>44484</v>
       </c>
       <c r="B419">
         <v>2021</v>
@@ -13927,12 +13930,76 @@
         <v>25</v>
       </c>
       <c r="H419">
+        <v>86</v>
+      </c>
+      <c r="I419">
+        <v>50</v>
+      </c>
+      <c r="J419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A420" s="1">
+        <v>44486</v>
+      </c>
+      <c r="B420">
+        <v>2021</v>
+      </c>
+      <c r="C420" t="s">
+        <v>26</v>
+      </c>
+      <c r="D420">
+        <v>3</v>
+      </c>
+      <c r="E420" t="s">
+        <v>14</v>
+      </c>
+      <c r="F420" t="s">
+        <v>20</v>
+      </c>
+      <c r="G420" t="s">
+        <v>24</v>
+      </c>
+      <c r="H420">
+        <v>74</v>
+      </c>
+      <c r="I420">
         <v>80</v>
       </c>
-      <c r="I419">
+      <c r="J420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A421" s="1">
+        <v>44486</v>
+      </c>
+      <c r="B421">
+        <v>2021</v>
+      </c>
+      <c r="C421" t="s">
+        <v>26</v>
+      </c>
+      <c r="D421">
+        <v>3</v>
+      </c>
+      <c r="E421" t="s">
+        <v>20</v>
+      </c>
+      <c r="F421" t="s">
+        <v>14</v>
+      </c>
+      <c r="G421" t="s">
+        <v>25</v>
+      </c>
+      <c r="H421">
+        <v>80</v>
+      </c>
+      <c r="I421">
         <v>74</v>
       </c>
-      <c r="J419">
+      <c r="J421">
         <v>0</v>
       </c>
     </row>
